--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>16.93679</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.61351</v>
+      </c>
+      <c r="E3" t="n">
         <v>16.7977</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16.93679</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.61351</v>
       </c>
       <c r="F3" t="n">
         <v>42.73683</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.96797</v>
+      </c>
+      <c r="D4" t="n">
         <v>16.79515</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>16.92068</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.96797</v>
       </c>
       <c r="F4" t="n">
         <v>42.71875</v>
